--- a/docs/assets/AddUsersTemplate.xlsx
+++ b/docs/assets/AddUsersTemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cisco-my.sharepoint.com/personal/vamelend_cisco_com/Documents/Desktop/wbx1/lab/LAB-1251/docs/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="8_{C7AFAEEE-363A-494D-85D2-9E4FCDE7751E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{151AFA02-EAA2-4F20-B3D2-E163E0F08E57}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="8_{C7AFAEEE-363A-494D-85D2-9E4FCDE7751E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54A6B0BE-3B98-4BF8-8825-E3F7A74C4274}"/>
   <bookViews>
-    <workbookView xWindow="630" yWindow="640" windowWidth="18570" windowHeight="10640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="START HERE" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="136">
   <si>
     <t>First Name</t>
   </si>
@@ -303,12 +303,6 @@
     <t>Taylor Bard</t>
   </si>
   <si>
-    <t>Sales2</t>
-  </si>
-  <si>
-    <t>Sales1</t>
-  </si>
-  <si>
     <t>Miami</t>
   </si>
   <si>
@@ -414,75 +408,6 @@
   </si>
   <si>
     <t>HQ</t>
-  </si>
-  <si>
-    <t>Factory</t>
-  </si>
-  <si>
-    <t>Sales1@YourFullName##.com</t>
-  </si>
-  <si>
-    <t>Sales2@YourFullName##.com</t>
-  </si>
-  <si>
-    <t>HQ Sales1</t>
-  </si>
-  <si>
-    <t>HQ Sales2</t>
-  </si>
-  <si>
-    <t>Marketing1</t>
-  </si>
-  <si>
-    <t>Marketing2</t>
-  </si>
-  <si>
-    <t>HQ Marketing1</t>
-  </si>
-  <si>
-    <t>HQ Marketing2</t>
-  </si>
-  <si>
-    <t>Marketing1@YourFullName##.com</t>
-  </si>
-  <si>
-    <t>Marketing2@YourFullName##.com</t>
-  </si>
-  <si>
-    <t>ProductDev1</t>
-  </si>
-  <si>
-    <t>ProductDev2</t>
-  </si>
-  <si>
-    <t>ProductDev3</t>
-  </si>
-  <si>
-    <t>ProductDev4</t>
-  </si>
-  <si>
-    <t>Factory ProductDev1</t>
-  </si>
-  <si>
-    <t>Factory ProductDev2</t>
-  </si>
-  <si>
-    <t>Factory ProductDev3</t>
-  </si>
-  <si>
-    <t>Factory ProductDev4</t>
-  </si>
-  <si>
-    <t>ProductDev1@YourFullName##.com</t>
-  </si>
-  <si>
-    <t>ProductDev2@YourFullName##.com</t>
-  </si>
-  <si>
-    <t>ProductDev3@YourFullName##.com</t>
-  </si>
-  <si>
-    <t>ProductDev4@YourFullName##.com</t>
   </si>
   <si>
     <t>Alternate Email 1</t>
@@ -1622,7 +1547,7 @@
     </row>
     <row r="4" spans="1:2" ht="21" x14ac:dyDescent="0.5">
       <c r="A4" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="21" x14ac:dyDescent="0.5">
@@ -1637,7 +1562,7 @@
     </row>
     <row r="7" spans="1:2" ht="42" x14ac:dyDescent="0.5">
       <c r="A7" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="21" x14ac:dyDescent="0.5">
@@ -1647,7 +1572,7 @@
     </row>
     <row r="9" spans="1:2" ht="21" x14ac:dyDescent="0.5">
       <c r="A9" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>22</v>
@@ -1716,7 +1641,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:BG17"/>
+  <dimension ref="A1:BG9"/>
   <sheetFormatPr defaultColWidth="11.1640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="14.1640625" bestFit="1" customWidth="1"/>
@@ -1762,16 +1687,16 @@
         <v>3</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="I2" s="10" t="s">
         <v>29</v>
@@ -1783,13 +1708,13 @@
         <v>31</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="M2" s="10" t="s">
         <v>32</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="O2" s="10" t="s">
         <v>33</v>
@@ -1825,106 +1750,106 @@
         <v>5</v>
       </c>
       <c r="Z2" s="14" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="AA2" s="14" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="AB2" s="14" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="AC2" s="14" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="AD2" s="14" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="AE2" s="14" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="AF2" s="14" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="AG2" s="14" t="s">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="AH2" s="14" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="AI2" s="14" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="AJ2" s="14" t="s">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="AK2" s="14" t="s">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="AL2" s="14" t="s">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="AM2" s="14" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="AN2" s="14" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="AO2" s="14" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="AP2" s="14" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="AQ2" s="14" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="AR2" s="14" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="AS2" s="14" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="AT2" s="14" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="AU2" s="14" t="s">
         <v>7</v>
       </c>
       <c r="AV2" s="14" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="AW2" s="14" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="AX2" s="14" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="AY2" s="14" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="AZ2" s="13" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="BA2" s="13" t="s">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="BB2" s="13" t="s">
-        <v>151</v>
+        <v>126</v>
       </c>
       <c r="BC2" s="13" t="s">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="BD2" s="13" t="s">
-        <v>153</v>
+        <v>128</v>
       </c>
       <c r="BE2" s="13" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="BF2" s="13" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="BG2" s="13" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:59" x14ac:dyDescent="0.35">
@@ -1938,7 +1863,7 @@
         <v>48</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
@@ -1967,7 +1892,7 @@
         <v>47</v>
       </c>
       <c r="Y3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="AH3" t="b">
         <v>0</v>
@@ -1979,7 +1904,7 @@
         <v>0</v>
       </c>
       <c r="AL3" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="AR3" t="b">
         <v>1</v>
@@ -2041,7 +1966,7 @@
         <v>51</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="E4" s="9"/>
       <c r="F4" s="9"/>
@@ -2070,7 +1995,7 @@
         <v>50</v>
       </c>
       <c r="Y4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="AH4" t="b">
         <v>0</v>
@@ -2082,7 +2007,7 @@
         <v>0</v>
       </c>
       <c r="AL4" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="AR4" t="b">
         <v>1</v>
@@ -2144,7 +2069,7 @@
         <v>54</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
@@ -2173,7 +2098,7 @@
         <v>53</v>
       </c>
       <c r="Y5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="AH5" t="b">
         <v>0</v>
@@ -2185,7 +2110,7 @@
         <v>0</v>
       </c>
       <c r="AL5" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="AR5" t="b">
         <v>1</v>
@@ -2247,7 +2172,7 @@
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
@@ -2262,7 +2187,7 @@
       <c r="O6" s="9"/>
       <c r="P6" s="9"/>
       <c r="Q6">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="R6" s="9"/>
       <c r="S6" s="9"/>
@@ -2276,7 +2201,7 @@
         <v>56</v>
       </c>
       <c r="Y6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AH6" t="b">
         <v>0</v>
@@ -2288,7 +2213,7 @@
         <v>0</v>
       </c>
       <c r="AL6" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="AR6" t="b">
         <v>1</v>
@@ -2350,7 +2275,7 @@
         <v>60</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -2365,7 +2290,7 @@
       <c r="O7" s="9"/>
       <c r="P7" s="9"/>
       <c r="Q7">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="R7" s="9"/>
       <c r="S7" s="9"/>
@@ -2379,7 +2304,7 @@
         <v>59</v>
       </c>
       <c r="Y7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AH7" t="b">
         <v>0</v>
@@ -2391,7 +2316,7 @@
         <v>0</v>
       </c>
       <c r="AL7" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="AR7" t="b">
         <v>1</v>
@@ -2453,7 +2378,7 @@
         <v>63</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
@@ -2468,7 +2393,7 @@
       <c r="O8" s="9"/>
       <c r="P8" s="9"/>
       <c r="Q8">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="R8" s="9"/>
       <c r="S8" s="9"/>
@@ -2482,7 +2407,7 @@
         <v>62</v>
       </c>
       <c r="Y8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AH8" t="b">
         <v>0</v>
@@ -2494,7 +2419,7 @@
         <v>0</v>
       </c>
       <c r="AL8" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="AR8" t="b">
         <v>1</v>
@@ -2556,7 +2481,7 @@
         <v>66</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
@@ -2571,7 +2496,7 @@
       <c r="O9" s="9"/>
       <c r="P9" s="9"/>
       <c r="Q9">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="R9" s="9"/>
       <c r="S9" s="9"/>
@@ -2585,7 +2510,7 @@
         <v>65</v>
       </c>
       <c r="Y9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AH9" t="b">
         <v>0</v>
@@ -2597,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="AL9" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="AR9" t="b">
         <v>1</v>
@@ -2645,830 +2570,6 @@
         <v>1</v>
       </c>
       <c r="BG9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:59" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>96</v>
-      </c>
-      <c r="B10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C10" t="s">
-        <v>100</v>
-      </c>
-      <c r="D10" t="s">
-        <v>98</v>
-      </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="9"/>
-      <c r="Q10">
-        <v>105</v>
-      </c>
-      <c r="R10" s="9"/>
-      <c r="S10" s="9"/>
-      <c r="T10" s="9"/>
-      <c r="U10" s="9"/>
-      <c r="V10" s="9"/>
-      <c r="W10" t="s">
-        <v>96</v>
-      </c>
-      <c r="X10" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>96</v>
-      </c>
-      <c r="AH10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="s">
-        <v>156</v>
-      </c>
-      <c r="AR10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AS10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AT10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AU10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="b">
-        <v>1</v>
-      </c>
-      <c r="BA10" t="b">
-        <v>1</v>
-      </c>
-      <c r="BB10" t="b">
-        <v>0</v>
-      </c>
-      <c r="BC10" t="b">
-        <v>0</v>
-      </c>
-      <c r="BD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="BE10" t="b">
-        <v>1</v>
-      </c>
-      <c r="BF10" t="b">
-        <v>1</v>
-      </c>
-      <c r="BG10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:59" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>96</v>
-      </c>
-      <c r="B11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" t="s">
-        <v>101</v>
-      </c>
-      <c r="D11" t="s">
-        <v>99</v>
-      </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
-      <c r="Q11">
-        <v>106</v>
-      </c>
-      <c r="R11" s="9"/>
-      <c r="S11" s="9"/>
-      <c r="T11" s="9"/>
-      <c r="U11" s="9"/>
-      <c r="V11" s="9"/>
-      <c r="W11" t="s">
-        <v>96</v>
-      </c>
-      <c r="X11" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>96</v>
-      </c>
-      <c r="AH11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="s">
-        <v>156</v>
-      </c>
-      <c r="AR11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AS11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AT11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AU11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AZ11" t="b">
-        <v>1</v>
-      </c>
-      <c r="BA11" t="b">
-        <v>1</v>
-      </c>
-      <c r="BB11" t="b">
-        <v>0</v>
-      </c>
-      <c r="BC11" t="b">
-        <v>0</v>
-      </c>
-      <c r="BD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="BE11" t="b">
-        <v>1</v>
-      </c>
-      <c r="BF11" t="b">
-        <v>1</v>
-      </c>
-      <c r="BG11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:59" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B12" t="s">
-        <v>102</v>
-      </c>
-      <c r="C12" t="s">
-        <v>104</v>
-      </c>
-      <c r="D12" t="s">
-        <v>106</v>
-      </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
-      <c r="Q12">
-        <v>107</v>
-      </c>
-      <c r="R12" s="9"/>
-      <c r="S12" s="9"/>
-      <c r="T12" s="9"/>
-      <c r="U12" s="9"/>
-      <c r="V12" s="9"/>
-      <c r="W12" t="s">
-        <v>96</v>
-      </c>
-      <c r="X12" t="s">
-        <v>102</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>96</v>
-      </c>
-      <c r="AH12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="s">
-        <v>156</v>
-      </c>
-      <c r="AR12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AS12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AT12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AU12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="b">
-        <v>1</v>
-      </c>
-      <c r="BA12" t="b">
-        <v>1</v>
-      </c>
-      <c r="BB12" t="b">
-        <v>0</v>
-      </c>
-      <c r="BC12" t="b">
-        <v>0</v>
-      </c>
-      <c r="BD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="BE12" t="b">
-        <v>1</v>
-      </c>
-      <c r="BF12" t="b">
-        <v>1</v>
-      </c>
-      <c r="BG12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:59" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>96</v>
-      </c>
-      <c r="B13" t="s">
-        <v>103</v>
-      </c>
-      <c r="C13" t="s">
-        <v>105</v>
-      </c>
-      <c r="D13" t="s">
-        <v>107</v>
-      </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="9"/>
-      <c r="Q13">
-        <v>108</v>
-      </c>
-      <c r="R13" s="9"/>
-      <c r="S13" s="9"/>
-      <c r="T13" s="9"/>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" t="s">
-        <v>96</v>
-      </c>
-      <c r="X13" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>96</v>
-      </c>
-      <c r="AH13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="s">
-        <v>156</v>
-      </c>
-      <c r="AR13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AS13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AT13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AU13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="b">
-        <v>1</v>
-      </c>
-      <c r="BA13" t="b">
-        <v>1</v>
-      </c>
-      <c r="BB13" t="b">
-        <v>0</v>
-      </c>
-      <c r="BC13" t="b">
-        <v>0</v>
-      </c>
-      <c r="BD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="BE13" t="b">
-        <v>1</v>
-      </c>
-      <c r="BF13" t="b">
-        <v>1</v>
-      </c>
-      <c r="BG13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:59" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>97</v>
-      </c>
-      <c r="B14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C14" t="s">
-        <v>112</v>
-      </c>
-      <c r="D14" t="s">
-        <v>116</v>
-      </c>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="9"/>
-      <c r="Q14">
-        <v>105</v>
-      </c>
-      <c r="R14" s="9"/>
-      <c r="S14" s="9"/>
-      <c r="T14" s="9"/>
-      <c r="U14" s="9"/>
-      <c r="V14" s="9"/>
-      <c r="W14" t="s">
-        <v>97</v>
-      </c>
-      <c r="X14" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="s">
-        <v>156</v>
-      </c>
-      <c r="AR14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AS14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AT14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AU14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AV14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AZ14" t="b">
-        <v>1</v>
-      </c>
-      <c r="BA14" t="b">
-        <v>1</v>
-      </c>
-      <c r="BB14" t="b">
-        <v>0</v>
-      </c>
-      <c r="BC14" t="b">
-        <v>0</v>
-      </c>
-      <c r="BD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="BE14" t="b">
-        <v>1</v>
-      </c>
-      <c r="BF14" t="b">
-        <v>1</v>
-      </c>
-      <c r="BG14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:59" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>97</v>
-      </c>
-      <c r="B15" t="s">
-        <v>109</v>
-      </c>
-      <c r="C15" t="s">
-        <v>113</v>
-      </c>
-      <c r="D15" t="s">
-        <v>117</v>
-      </c>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
-      <c r="P15" s="9"/>
-      <c r="Q15">
-        <v>106</v>
-      </c>
-      <c r="R15" s="9"/>
-      <c r="S15" s="9"/>
-      <c r="T15" s="9"/>
-      <c r="U15" s="9"/>
-      <c r="V15" s="9"/>
-      <c r="W15" t="s">
-        <v>97</v>
-      </c>
-      <c r="X15" t="s">
-        <v>109</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="s">
-        <v>156</v>
-      </c>
-      <c r="AR15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AS15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AT15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AU15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AZ15" t="b">
-        <v>1</v>
-      </c>
-      <c r="BA15" t="b">
-        <v>1</v>
-      </c>
-      <c r="BB15" t="b">
-        <v>0</v>
-      </c>
-      <c r="BC15" t="b">
-        <v>0</v>
-      </c>
-      <c r="BD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="BE15" t="b">
-        <v>1</v>
-      </c>
-      <c r="BF15" t="b">
-        <v>1</v>
-      </c>
-      <c r="BG15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:59" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>97</v>
-      </c>
-      <c r="B16" t="s">
-        <v>110</v>
-      </c>
-      <c r="C16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D16" t="s">
-        <v>118</v>
-      </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="9"/>
-      <c r="Q16">
-        <v>107</v>
-      </c>
-      <c r="R16" s="9"/>
-      <c r="S16" s="9"/>
-      <c r="T16" s="9"/>
-      <c r="U16" s="9"/>
-      <c r="V16" s="9"/>
-      <c r="W16" t="s">
-        <v>97</v>
-      </c>
-      <c r="X16" t="s">
-        <v>110</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="s">
-        <v>156</v>
-      </c>
-      <c r="AR16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AS16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AT16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AU16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AZ16" t="b">
-        <v>1</v>
-      </c>
-      <c r="BA16" t="b">
-        <v>1</v>
-      </c>
-      <c r="BB16" t="b">
-        <v>0</v>
-      </c>
-      <c r="BC16" t="b">
-        <v>0</v>
-      </c>
-      <c r="BD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="BE16" t="b">
-        <v>1</v>
-      </c>
-      <c r="BF16" t="b">
-        <v>1</v>
-      </c>
-      <c r="BG16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:59" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>97</v>
-      </c>
-      <c r="B17" t="s">
-        <v>111</v>
-      </c>
-      <c r="C17" t="s">
-        <v>115</v>
-      </c>
-      <c r="D17" t="s">
-        <v>119</v>
-      </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="9"/>
-      <c r="Q17">
-        <v>108</v>
-      </c>
-      <c r="R17" s="9"/>
-      <c r="S17" s="9"/>
-      <c r="T17" s="9"/>
-      <c r="U17" s="9"/>
-      <c r="V17" s="9"/>
-      <c r="W17" t="s">
-        <v>97</v>
-      </c>
-      <c r="X17" t="s">
-        <v>111</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="s">
-        <v>156</v>
-      </c>
-      <c r="AR17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AS17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AT17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AU17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AZ17" t="b">
-        <v>1</v>
-      </c>
-      <c r="BA17" t="b">
-        <v>1</v>
-      </c>
-      <c r="BB17" t="b">
-        <v>0</v>
-      </c>
-      <c r="BC17" t="b">
-        <v>0</v>
-      </c>
-      <c r="BD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="BE17" t="b">
-        <v>1</v>
-      </c>
-      <c r="BF17" t="b">
-        <v>1</v>
-      </c>
-      <c r="BG17" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3548,7 +2649,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
@@ -3563,14 +2664,14 @@
       </c>
       <c r="G3" s="8"/>
       <c r="H3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
@@ -3585,14 +2686,14 @@
       </c>
       <c r="G4" s="8"/>
       <c r="H4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
@@ -3607,14 +2708,14 @@
       </c>
       <c r="G5" s="8"/>
       <c r="H5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="12" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
@@ -3629,14 +2730,14 @@
       </c>
       <c r="G6" s="8"/>
       <c r="H6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B7" t="s">
         <v>19</v>
@@ -3651,14 +2752,14 @@
       </c>
       <c r="G7" s="8"/>
       <c r="H7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B8" t="s">
         <v>19</v>
@@ -3673,14 +2774,14 @@
       </c>
       <c r="G8" s="8"/>
       <c r="H8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I8" s="9"/>
       <c r="J8" s="9"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B9" t="s">
         <v>19</v>
@@ -3695,14 +2796,14 @@
       </c>
       <c r="G9" s="8"/>
       <c r="H9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
@@ -3717,14 +2818,14 @@
       </c>
       <c r="G10" s="8"/>
       <c r="H10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I10" s="9"/>
       <c r="J10" s="9"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B11" t="s">
         <v>19</v>
@@ -3746,7 +2847,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B12" t="s">
         <v>19</v>
@@ -3768,7 +2869,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B13" t="s">
         <v>19</v>
@@ -3790,7 +2891,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B14" t="s">
         <v>19</v>
@@ -3812,7 +2913,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B15" t="s">
         <v>19</v>
@@ -3834,7 +2935,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B16" t="s">
         <v>19</v>
@@ -3856,7 +2957,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B17" t="s">
         <v>19</v>
@@ -3878,7 +2979,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B18" t="s">
         <v>19</v>
@@ -3900,7 +3001,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B19" t="s">
         <v>19</v>
@@ -3922,7 +3023,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B20" t="s">
         <v>19</v>
@@ -3944,7 +3045,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B21" t="s">
         <v>19</v>
@@ -3959,14 +3060,14 @@
       </c>
       <c r="G21" s="8"/>
       <c r="H21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I21" s="9"/>
       <c r="J21" s="9"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B22" t="s">
         <v>19</v>
@@ -3981,14 +3082,14 @@
       </c>
       <c r="G22" s="8"/>
       <c r="H22" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I22" s="9"/>
       <c r="J22" s="9"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B23" t="s">
         <v>19</v>
@@ -4003,14 +3104,14 @@
       </c>
       <c r="G23" s="8"/>
       <c r="H23" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I23" s="9"/>
       <c r="J23" s="9"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B24" t="s">
         <v>19</v>
@@ -4025,7 +3126,7 @@
       </c>
       <c r="G24" s="8"/>
       <c r="H24" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I24" s="9"/>
       <c r="J24" s="9"/>
@@ -4039,4 +3140,10 @@
     <oddFooter>&amp;R_x000D_&amp;1#&amp;"Calibri"&amp;8&amp;K000000 Cisco Confidential</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{c8f49a32-fde3-48a5-9266-b5b0972a22dc}" enabled="1" method="Standard" siteId="{5ae1af62-9505-4097-a69a-c1553ef7840e}" removed="0"/>
+</clbl:labelList>
 </file>